--- a/artfynd/A 45815-2025 artfynd.xlsx
+++ b/artfynd/A 45815-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>93143059</v>
+        <v>135292182</v>
       </c>
       <c r="B2" t="n">
-        <v>101897</v>
+        <v>97435</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,49 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220075</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gullpudra</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chrysosplenium alternifolium</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>med groddkorn</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Axebovägen, Sjöarp, Ög</t>
+          <t>Holtäppan, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>517171</v>
+        <v>517266</v>
       </c>
       <c r="R2" t="n">
-        <v>6399541</v>
+        <v>6399801</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,12 +752,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-05-07</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-05-07</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -754,21 +776,986 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>William Rosén</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>William Rosén</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>135292273</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Holtäppan, Ög</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>517266</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6399770</v>
+      </c>
+      <c r="S3" t="n">
+        <v>7</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Ydre</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Svinhult</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Flög iväg mot nordöst när jag kom dit</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>William Rosén</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>William Rosén</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>93143059</v>
+      </c>
+      <c r="B4" t="n">
+        <v>101897</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220075</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Gullpudra</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Chrysosplenium alternifolium</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Axebovägen, Sjöarp, Ög</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>517171</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6399541</v>
+      </c>
+      <c r="S4" t="n">
+        <v>15</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ydre</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Svinhult</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2021-05-07</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2021-05-07</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
           <t>David Ek</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX4" t="inlineStr">
         <is>
           <t>David Ek</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>135292197</v>
+      </c>
+      <c r="B5" t="n">
+        <v>111153</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220240</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Linnea</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Linnaea borealis</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Holtäppan, Ög</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>517266</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6399770</v>
+      </c>
+      <c r="S5" t="n">
+        <v>7</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ydre</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Svinhult</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>William Rosén</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>William Rosén</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>135292109</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Holtäppan, Ög</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>517366</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6399709</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ydre</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Svinhult</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>William Rosén</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>William Rosén</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>135292168</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Holtäppan, Ög</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>517299</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6399708</v>
+      </c>
+      <c r="S7" t="n">
+        <v>8</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ydre</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Svinhult</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>William Rosén</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>William Rosén</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>135292018</v>
+      </c>
+      <c r="B8" t="n">
+        <v>106324</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Holtäppan, Ög</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>517299</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6399708</v>
+      </c>
+      <c r="S8" t="n">
+        <v>8</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ydre</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Svinhult</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>William Rosén</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>William Rosén</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>135292073</v>
+      </c>
+      <c r="B9" t="n">
+        <v>98062</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>224363</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Vanlig revlummer</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Holtäppan, Ög</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>517299</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6399708</v>
+      </c>
+      <c r="S9" t="n">
+        <v>8</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ydre</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Svinhult</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>William Rosén</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>William Rosén</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>135292096</v>
+      </c>
+      <c r="B10" t="n">
+        <v>98062</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>224363</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Vanlig revlummer</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Holtäppan, Ög</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>517366</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6399678</v>
+      </c>
+      <c r="S10" t="n">
+        <v>7</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ydre</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Svinhult</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>13:43</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>13:43</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>William Rosén</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>William Rosén</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 45815-2025 artfynd.xlsx
+++ b/artfynd/A 45815-2025 artfynd.xlsx
@@ -904,7 +904,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Flög iväg mot nordöst när jag kom dit</t>
+          <t>Flög iväg mot norr när jag kom dit</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1314,6 +1314,7 @@
           <t>blomknopp</t>
         </is>
       </c>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1325,13 +1326,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>517299</v>
+        <v>517332</v>
       </c>
       <c r="R7" t="n">
-        <v>6399708</v>
+        <v>6399730</v>
       </c>
       <c r="S7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1379,6 +1380,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1440,6 +1442,7 @@
           <t>blomning</t>
         </is>
       </c>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1451,13 +1454,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>517299</v>
+        <v>517332</v>
       </c>
       <c r="R8" t="n">
-        <v>6399708</v>
+        <v>6399709</v>
       </c>
       <c r="S8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1505,6 +1508,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 45815-2025 artfynd.xlsx
+++ b/artfynd/A 45815-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -792,6 +797,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135292182</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -928,6 +938,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135292273</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1025,6 +1040,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93143059</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1147,6 +1167,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135292197</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1268,6 +1293,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135292109</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1396,6 +1426,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135292168</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1524,6 +1559,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135292018</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1642,6 +1682,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135292073</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1760,8 +1805,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135292096</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 45815-2025 artfynd.xlsx
+++ b/artfynd/A 45815-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135292182</v>
       </c>
       <c r="B2" t="n">
-        <v>97435</v>
+        <v>97479</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -808,7 +808,7 @@
         <v>135292273</v>
       </c>
       <c r="B3" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1051,7 +1051,7 @@
         <v>135292197</v>
       </c>
       <c r="B5" t="n">
-        <v>111153</v>
+        <v>111210</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         <v>135292109</v>
       </c>
       <c r="B6" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
         <v>135292168</v>
       </c>
       <c r="B7" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>135292018</v>
       </c>
       <c r="B8" t="n">
-        <v>106324</v>
+        <v>106379</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         <v>135292073</v>
       </c>
       <c r="B9" t="n">
-        <v>98062</v>
+        <v>98106</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>135292096</v>
       </c>
       <c r="B10" t="n">
-        <v>98062</v>
+        <v>98106</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 45815-2025 artfynd.xlsx
+++ b/artfynd/A 45815-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135292182</v>
       </c>
       <c r="B2" t="n">
-        <v>97479</v>
+        <v>97506</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1051,7 +1051,7 @@
         <v>135292197</v>
       </c>
       <c r="B5" t="n">
-        <v>111210</v>
+        <v>111237</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         <v>135292109</v>
       </c>
       <c r="B6" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
         <v>135292168</v>
       </c>
       <c r="B7" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>135292018</v>
       </c>
       <c r="B8" t="n">
-        <v>106379</v>
+        <v>106406</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         <v>135292073</v>
       </c>
       <c r="B9" t="n">
-        <v>98106</v>
+        <v>98133</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>135292096</v>
       </c>
       <c r="B10" t="n">
-        <v>98106</v>
+        <v>98133</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 45815-2025 artfynd.xlsx
+++ b/artfynd/A 45815-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>93143059</v>
+        <v>135292182</v>
       </c>
       <c r="B2" t="n">
-        <v>101897</v>
+        <v>97511</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +691,49 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220075</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gullpudra</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chrysosplenium alternifolium</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>med groddkorn</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Axebovägen, Sjöarp, Ög</t>
+          <t>Holtäppan, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>517171</v>
+        <v>517266</v>
       </c>
       <c r="R2" t="n">
-        <v>6399541</v>
+        <v>6399801</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +757,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-05-07</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-05-07</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -759,30 +781,1047 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>David Ek</t>
+          <t>William Rosén</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>David Ek</t>
+          <t>William Rosén</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/135292182</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>135292273</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Holtäppan, Ög</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>517266</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6399770</v>
+      </c>
+      <c r="S3" t="n">
+        <v>7</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Ydre</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Svinhult</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Flög iväg mot norr när jag kom dit</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>William Rosén</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>William Rosén</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135292273</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>93143059</v>
+      </c>
+      <c r="B4" t="n">
+        <v>101897</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220075</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Gullpudra</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Chrysosplenium alternifolium</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Axebovägen, Sjöarp, Ög</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>517171</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6399541</v>
+      </c>
+      <c r="S4" t="n">
+        <v>15</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ydre</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Svinhult</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2021-05-07</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2021-05-07</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>David Ek</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>David Ek</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/93143059</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>135292197</v>
+      </c>
+      <c r="B5" t="n">
+        <v>111242</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220240</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Linnea</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Linnaea borealis</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Holtäppan, Ög</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>517266</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6399770</v>
+      </c>
+      <c r="S5" t="n">
+        <v>7</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ydre</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Svinhult</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>William Rosén</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>William Rosén</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135292197</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>135292109</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Holtäppan, Ög</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>517366</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6399709</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ydre</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Svinhult</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>William Rosén</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>William Rosén</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135292109</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>135292168</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Holtäppan, Ög</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>517332</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6399730</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ydre</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Svinhult</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>William Rosén</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>William Rosén</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135292168</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>135292018</v>
+      </c>
+      <c r="B8" t="n">
+        <v>106411</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Holtäppan, Ög</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>517332</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6399709</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ydre</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Svinhult</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>William Rosén</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>William Rosén</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135292018</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>135292073</v>
+      </c>
+      <c r="B9" t="n">
+        <v>98138</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>224363</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Vanlig revlummer</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Holtäppan, Ög</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>517299</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6399708</v>
+      </c>
+      <c r="S9" t="n">
+        <v>8</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ydre</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Svinhult</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>William Rosén</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>William Rosén</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135292073</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>135292096</v>
+      </c>
+      <c r="B10" t="n">
+        <v>98138</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>224363</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Vanlig revlummer</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Holtäppan, Ög</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>517366</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6399678</v>
+      </c>
+      <c r="S10" t="n">
+        <v>7</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ydre</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Svinhult</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>13:43</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>13:43</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>William Rosén</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>William Rosén</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135292096</t>
         </is>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 45815-2025 artfynd.xlsx
+++ b/artfynd/A 45815-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135292182</v>
       </c>
       <c r="B2" t="n">
-        <v>97511</v>
+        <v>97513</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1051,7 +1051,7 @@
         <v>135292197</v>
       </c>
       <c r="B5" t="n">
-        <v>111242</v>
+        <v>111244</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         <v>135292109</v>
       </c>
       <c r="B6" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
         <v>135292168</v>
       </c>
       <c r="B7" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>135292018</v>
       </c>
       <c r="B8" t="n">
-        <v>106411</v>
+        <v>106413</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         <v>135292073</v>
       </c>
       <c r="B9" t="n">
-        <v>98138</v>
+        <v>98140</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>135292096</v>
       </c>
       <c r="B10" t="n">
-        <v>98138</v>
+        <v>98140</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
